--- a/artfynd/A 37023-2021 artfynd.xlsx
+++ b/artfynd/A 37023-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37023-2021 artfynd.xlsx
+++ b/artfynd/A 37023-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5607,6 +5607,260 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>118957141</v>
+      </c>
+      <c r="B41" t="n">
+        <v>97831</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>A 37023, Bjärka, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>573990</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6405170</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>118957178</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97831</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>A 37023, Bjärka, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>574038</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6405216</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37023-2021 artfynd.xlsx
+++ b/artfynd/A 37023-2021 artfynd.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 37023-2021 artfynd.xlsx
+++ b/artfynd/A 37023-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87563738</v>
+        <v>95065184</v>
       </c>
       <c r="B2" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Smedserumskogen, Sm</t>
+          <t>Smedserum, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573821.5765057928</v>
+        <v>574019</v>
       </c>
       <c r="R2" t="n">
-        <v>6405050.316059822</v>
+        <v>6405177</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,72 +787,66 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>87563791</v>
+        <v>96288664</v>
       </c>
       <c r="B3" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>5733</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Smedsrumskogen, Sm</t>
+          <t>Smedserum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573858.9104453641</v>
+        <v>573891</v>
       </c>
       <c r="R3" t="n">
-        <v>6405199.795037965</v>
+        <v>6405203</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,22 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,84 +884,81 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87563808</v>
+        <v>96288620</v>
       </c>
       <c r="B4" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>5741</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Smedsumskogen, Sm</t>
+          <t>Smedserum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573845.4955918008</v>
+        <v>573867</v>
       </c>
       <c r="R4" t="n">
-        <v>6405144.618378707</v>
+        <v>6405163</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,22 +982,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,84 +996,81 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87563751</v>
+        <v>96288631</v>
       </c>
       <c r="B5" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>5741</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Smedserumskogen, Sm</t>
+          <t>Smedserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573821.5765057928</v>
+        <v>573834</v>
       </c>
       <c r="R5" t="n">
-        <v>6405050.316059822</v>
+        <v>6405178</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,22 +1094,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,34 +1108,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95065184</v>
+        <v>96288641</v>
       </c>
       <c r="B6" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>5741</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1215,21 +1165,21 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Smedserum, Bjärka, Sm</t>
+          <t>Smedserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574019.1000337133</v>
+        <v>573822</v>
       </c>
       <c r="R6" t="n">
-        <v>6405176.60464553</v>
+        <v>6405222</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,22 +1206,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,81 +1220,78 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95065361</v>
+        <v>96288649</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5741</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Smedserum, Bjärka, Sm</t>
+          <t>Smedserum, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573877.6603656161</v>
+        <v>573829</v>
       </c>
       <c r="R7" t="n">
-        <v>6405226.270796916</v>
+        <v>6405238</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1381,22 +1318,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,81 +1332,78 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95065347</v>
+        <v>96193773</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Smedserum, Bjärka, Sm</t>
+          <t>A37023, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573991.5790309811</v>
+        <v>573738</v>
       </c>
       <c r="R8" t="n">
-        <v>6405162.232813665</v>
+        <v>6405105</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1506,22 +1430,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1549,65 +1463,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95065155</v>
+        <v>96193827</v>
       </c>
       <c r="B9" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Smedserum, Bjärka, Sm</t>
+          <t>A37023, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573992.4415971588</v>
+        <v>573811</v>
       </c>
       <c r="R9" t="n">
-        <v>6405173.448138639</v>
+        <v>6405110</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1631,27 +1539,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>4 med blommor + 2 med blad</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1679,62 +1572,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95065322</v>
+        <v>96288678</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Smedserum, Bjärka, Sm</t>
+          <t>Smedserum, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>573858.6524711855</v>
+        <v>573963</v>
       </c>
       <c r="R10" t="n">
-        <v>6405242.987643931</v>
+        <v>6405196</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1761,22 +1648,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1785,34 +1662,32 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96193827</v>
+        <v>96192459</v>
       </c>
       <c r="B11" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,26 +1695,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>6031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1855,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>573810.8572093324</v>
+        <v>573800</v>
       </c>
       <c r="R11" t="n">
-        <v>6405110.384581259</v>
+        <v>6405195</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1888,19 +1763,9 @@
           <t>2021-09-19</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1931,12 +1796,7 @@
         <v>96192518</v>
       </c>
       <c r="B12" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1979,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>573792.2595379602</v>
+        <v>573792</v>
       </c>
       <c r="R12" t="n">
-        <v>6405192.173355122</v>
+        <v>6405192</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2012,19 +1872,9 @@
           <t>2021-09-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2052,15 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96193773</v>
+        <v>96193903</v>
       </c>
       <c r="B13" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,26 +1913,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>6031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2103,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>573738.280194663</v>
+        <v>573826</v>
       </c>
       <c r="R13" t="n">
-        <v>6405105.321642731</v>
+        <v>6405134</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2136,19 +1981,9 @@
           <t>2021-09-19</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2176,15 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96193903</v>
+        <v>96194129</v>
       </c>
       <c r="B14" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,13 +2057,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>573825.9274452023</v>
+        <v>574034</v>
       </c>
       <c r="R14" t="n">
-        <v>6405133.59333244</v>
+        <v>6405192</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2260,19 +2090,9 @@
           <t>2021-09-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2300,65 +2120,61 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96193994</v>
+        <v>101996724</v>
       </c>
       <c r="B15" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221946</v>
+        <v>102018</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A37023, Bjärka, Sm</t>
+          <t>A 30023, Smedserum, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>573876.3160978918</v>
+        <v>574042</v>
       </c>
       <c r="R15" t="n">
-        <v>6405183.04860733</v>
+        <v>6405239</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2382,22 +2198,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2418,72 +2224,68 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96194033</v>
+        <v>101996718</v>
       </c>
       <c r="B16" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45046</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221946</v>
+        <v>102020</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A37023, Bjärka, Sm</t>
+          <t>A 30023, Smedserum, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>573886.1166238851</v>
+        <v>574042</v>
       </c>
       <c r="R16" t="n">
-        <v>6405173.0956136</v>
+        <v>6405239</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2507,22 +2309,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2543,22 +2335,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96194129</v>
+        <v>87563738</v>
       </c>
       <c r="B17" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2566,48 +2353,49 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6031</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A37023, Bjärka, Sm</t>
+          <t>Smedserumskogen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574033.7817222017</v>
+        <v>573822</v>
       </c>
       <c r="R17" t="n">
-        <v>6405191.807142118</v>
+        <v>6405050</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2631,22 +2419,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2667,22 +2455,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96192459</v>
+        <v>95065155</v>
       </c>
       <c r="B18" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,48 +2473,49 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6031</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A37023, Bjärka, Sm</t>
+          <t>Smedserum, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>573800.2228723746</v>
+        <v>573992</v>
       </c>
       <c r="R18" t="n">
-        <v>6405194.985822966</v>
+        <v>6405173</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2755,22 +2539,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>4 med blommor + 2 med blad</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2798,64 +2587,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96288664</v>
+        <v>102492499</v>
       </c>
       <c r="B19" t="n">
-        <v>88935</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5733</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Smedserum, Sm</t>
+          <t>Smedserum, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>573891.9980933786</v>
+        <v>573856</v>
       </c>
       <c r="R19" t="n">
-        <v>6405202.002018078</v>
+        <v>6405055</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2879,22 +2664,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2903,37 +2678,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96288641</v>
+        <v>118957141</v>
       </c>
       <c r="B20" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,45 +2708,50 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5741</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Smedserum, Sm</t>
+          <t>A 37023, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>573821.6439058066</v>
+        <v>573990</v>
       </c>
       <c r="R20" t="n">
-        <v>6405221.510294022</v>
+        <v>6405170</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3006,22 +2778,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3030,37 +2802,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96288649</v>
+        <v>118957178</v>
       </c>
       <c r="B21" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3068,45 +2832,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5741</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Smedserum, Sm</t>
+          <t>A 37023, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>573828.2749484004</v>
+        <v>574038</v>
       </c>
       <c r="R21" t="n">
-        <v>6405238.697446094</v>
+        <v>6405216</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3133,22 +2898,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3157,83 +2922,76 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96288631</v>
+        <v>95065078</v>
       </c>
       <c r="B22" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5741</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Smedserum, Sm</t>
+          <t>Smedserum, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>573833.1381375049</v>
+        <v>573992</v>
       </c>
       <c r="R22" t="n">
-        <v>6405177.456881729</v>
+        <v>6405217</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3260,22 +3018,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3284,83 +3042,76 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96288678</v>
+        <v>95065322</v>
       </c>
       <c r="B23" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Smedserum, Sm</t>
+          <t>Smedserum, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>573963.1666679846</v>
+        <v>573859</v>
       </c>
       <c r="R23" t="n">
-        <v>6405196.375743225</v>
+        <v>6405243</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3387,22 +3138,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3411,83 +3162,76 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96288620</v>
+        <v>95065347</v>
       </c>
       <c r="B24" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5741</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Smedserum, Sm</t>
+          <t>Smedserum, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>573867.5974634415</v>
+        <v>573992</v>
       </c>
       <c r="R24" t="n">
-        <v>6405163.156296945</v>
+        <v>6405162</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3514,22 +3258,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3538,88 +3282,79 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>101996718</v>
+        <v>95065361</v>
       </c>
       <c r="B25" t="n">
-        <v>44332</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102020</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 30023, Smedserum, Bjärka, Sm</t>
+          <t>Smedserum, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574042.5336405911</v>
+        <v>573878</v>
       </c>
       <c r="R25" t="n">
-        <v>6405238.898674257</v>
+        <v>6405226</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3643,22 +3378,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3679,65 +3414,60 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>101996493</v>
+        <v>95065377</v>
       </c>
       <c r="B26" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 37023, Smedserum, Bjärka, Sm</t>
+          <t>Smedserum, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>573883.2600140873</v>
+        <v>573956</v>
       </c>
       <c r="R26" t="n">
-        <v>6405183.176016404</v>
+        <v>6405219</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3764,27 +3494,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1-2 kvadratmeter</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3805,44 +3530,39 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>101996513</v>
+        <v>96193696</v>
       </c>
       <c r="B27" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3852,7 +3572,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3860,17 +3580,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 37023, Smedserum, Bjärka, Sm</t>
+          <t>A37023, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>573863.8621511303</v>
+        <v>573706</v>
       </c>
       <c r="R27" t="n">
-        <v>6405133.755717297</v>
+        <v>6405194</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3894,27 +3614,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Utmärkt med röd snitsel</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3935,22 +3640,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>101996285</v>
+        <v>101996224</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3975,13 +3675,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3990,10 +3698,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>573888.8969069695</v>
+        <v>574018</v>
       </c>
       <c r="R28" t="n">
-        <v>6405225.41038112</v>
+        <v>6405203</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4023,24 +3731,14 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Utmärkt av sks.</t>
+          <t>3 fjolårs, 5 knoppar. Röd snitsel.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4068,15 +3766,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>101996333</v>
+        <v>101996285</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4116,10 +3809,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>573849.5232105851</v>
+        <v>573889</v>
       </c>
       <c r="R29" t="n">
-        <v>6405245.486679364</v>
+        <v>6405225</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4149,24 +3842,14 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Utmärkt röd snitsel, sks</t>
+          <t>Utmärkt av sks.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4194,15 +3877,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>101996567</v>
+        <v>101996333</v>
       </c>
       <c r="B30" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4227,11 +3905,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -4242,14 +3916,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 37023, Smedserum, Bjärka, Sm</t>
+          <t>Smedserum, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>573885.1833525107</v>
+        <v>573850</v>
       </c>
       <c r="R30" t="n">
-        <v>6405253.073746311</v>
+        <v>6405245</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4279,24 +3953,14 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Utmärkt med rött plastband.</t>
+          <t>Utmärkt röd snitsel, sks</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4317,7 +3981,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4327,12 +3991,7 @@
         <v>101996401</v>
       </c>
       <c r="B31" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4372,10 +4031,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>573848.5624890302</v>
+        <v>573849</v>
       </c>
       <c r="R31" t="n">
-        <v>6405239.602784851</v>
+        <v>6405240</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4405,19 +4064,9 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4450,66 +4099,60 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>101996724</v>
+        <v>101996529</v>
       </c>
       <c r="B32" t="n">
-        <v>44330</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102018</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 30023, Smedserum, Bjärka, Sm</t>
+          <t>A 37023, Smedserum, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574042.5336405911</v>
+        <v>573820</v>
       </c>
       <c r="R32" t="n">
-        <v>6405238.898674257</v>
+        <v>6405201</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4536,19 +4179,14 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Utmärkt med röd sntsel</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4576,15 +4214,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>101996224</v>
+        <v>101996538</v>
       </c>
       <c r="B33" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4611,14 +4244,10 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>blomknopp</t>
@@ -4628,14 +4257,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Smedserum, Bjärka, Sm</t>
+          <t>A 37023, Smedserum, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574018.0856701223</v>
+        <v>573875</v>
       </c>
       <c r="R33" t="n">
-        <v>6405202.717972239</v>
+        <v>6405243</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4665,24 +4294,14 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>3 fjolårs, 5 knoppar. Röd snitsel.</t>
+          <t>2 knoppar, utmärkt med plastband</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4703,22 +4322,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>101996538</v>
+        <v>101996567</v>
       </c>
       <c r="B34" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4745,15 +4359,15 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4762,10 +4376,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>573874.676653911</v>
+        <v>573885</v>
       </c>
       <c r="R34" t="n">
-        <v>6405243.281614384</v>
+        <v>6405253</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4795,24 +4409,14 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>2 knoppar, utmärkt med plastband</t>
+          <t>Utmärkt med rött plastband.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4843,12 +4447,7 @@
         <v>101996596</v>
       </c>
       <c r="B35" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4892,10 +4491,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>573960.7558889571</v>
+        <v>573961</v>
       </c>
       <c r="R35" t="n">
-        <v>6405211.263954838</v>
+        <v>6405211</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4925,19 +4524,9 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4970,15 +4559,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>101996529</v>
+        <v>102604727</v>
       </c>
       <c r="B36" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5005,7 +4589,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5022,10 +4606,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>573819.8787499545</v>
+        <v>573811</v>
       </c>
       <c r="R36" t="n">
-        <v>6405201.212472258</v>
+        <v>6405188</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5052,27 +4636,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Utmärkt med röd sntsel</t>
+          <t>Röd snitsel fanns redan.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5093,72 +4667,71 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>102492499</v>
+        <v>102604772</v>
       </c>
       <c r="B37" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Smedserum, Bjärka, Sm</t>
+          <t>A 37023, Smedserum, Bjärka, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>573855.6946111257</v>
+        <v>573752</v>
       </c>
       <c r="R37" t="n">
-        <v>6405054.674950421</v>
+        <v>6405186</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5182,22 +4755,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5228,12 +4791,7 @@
         <v>102604808</v>
       </c>
       <c r="B38" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5277,10 +4835,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>573809.1503349791</v>
+        <v>573809</v>
       </c>
       <c r="R38" t="n">
-        <v>6405174.350565474</v>
+        <v>6405174</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5310,19 +4868,9 @@
           <t>2022-08-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5350,42 +4898,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>102604772</v>
+        <v>87563751</v>
       </c>
       <c r="B39" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5393,26 +4936,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>A 37023, Smedserum, Bjärka, Sm</t>
+          <t>Smedserumskogen, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>573752.3059931527</v>
+        <v>573822</v>
       </c>
       <c r="R39" t="n">
-        <v>6405185.574993777</v>
+        <v>6405050</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5436,22 +4975,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5472,49 +5011,44 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>102604727</v>
+        <v>87563768</v>
       </c>
       <c r="B40" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5527,17 +5061,17 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>A 37023, Smedserum, Bjärka, Sm</t>
+          <t>Smedserumskogen, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>573811.0328342972</v>
+        <v>573705</v>
       </c>
       <c r="R40" t="n">
-        <v>6405188.251015806</v>
+        <v>6405200</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5561,27 +5095,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Röd snitsel fanns redan.</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5602,22 +5131,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118957178</v>
+        <v>87563791</v>
       </c>
       <c r="B41" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5625,49 +5149,49 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>221946</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>A 37023, Bjärka, Sm</t>
+          <t>Smedsrumskogen, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574038</v>
+        <v>573859</v>
       </c>
       <c r="R41" t="n">
-        <v>6405216</v>
+        <v>6405200</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5691,22 +5215,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5727,22 +5251,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118957141</v>
+        <v>87563808</v>
       </c>
       <c r="B42" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5750,53 +5269,49 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>221946</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>A 37023, Bjärka, Sm</t>
+          <t>Smedsumskogen, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>573990</v>
+        <v>573845</v>
       </c>
       <c r="R42" t="n">
-        <v>6405170</v>
+        <v>6405145</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5820,22 +5335,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5856,10 +5371,456 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>96193994</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>A37023, Bjärka, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>573876</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6405183</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2021-09-19</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2021-09-19</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>96194033</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>A37023, Bjärka, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>573886</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6405173</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2021-09-19</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2021-09-19</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>101996493</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>A 37023, Smedserum, Bjärka, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>573883</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6405183</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1-2 kvadratmeter</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>101996513</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>A 37023, Smedserum, Bjärka, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>573864</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6405134</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Utmärkt med röd snitsel</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
